--- a/reports/Debug-purgatory-20260106/Week Total (Prior Year)_Visits.xlsx
+++ b/reports/Debug-purgatory-20260106/Week Total (Prior Year)_Visits.xlsx
@@ -37,13 +37,13 @@
     <t>Purgatory Tickets</t>
   </si>
   <si>
+    <t>Purgatory Coaster</t>
+  </si>
+  <si>
     <t>Purgatory Comp Tickets</t>
   </si>
   <si>
     <t>Purgatory Uplift Tickets</t>
-  </si>
-  <si>
-    <t>Purgatory Coaster</t>
   </si>
 </sst>
 </file>
@@ -588,10 +588,10 @@
         <v>1</v>
       </c>
       <c r="B13" s="2">
-        <v>45663</v>
+        <v>45664</v>
       </c>
       <c r="C13" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>5</v>
@@ -616,7 +616,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="2">
-        <v>45664</v>
+        <v>45665</v>
       </c>
       <c r="C15" s="2">
         <v>9</v>
@@ -630,13 +630,13 @@
         <v>1</v>
       </c>
       <c r="B16" s="2">
-        <v>45664</v>
+        <v>45665</v>
       </c>
       <c r="C16" s="2">
-        <v>2</v>
+        <v>995</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -647,7 +647,7 @@
         <v>45666</v>
       </c>
       <c r="C17" s="2">
-        <v>1</v>
+        <v>832</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>5</v>
@@ -661,7 +661,7 @@
         <v>45667</v>
       </c>
       <c r="C18" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>5</v>
@@ -675,7 +675,7 @@
         <v>45667</v>
       </c>
       <c r="C19" s="2">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>5</v>
@@ -686,10 +686,10 @@
         <v>1</v>
       </c>
       <c r="B20" s="2">
-        <v>45667</v>
+        <v>45668</v>
       </c>
       <c r="C20" s="2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>5</v>
@@ -703,10 +703,10 @@
         <v>45668</v>
       </c>
       <c r="C21" s="2">
-        <v>5</v>
+        <v>988</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -714,10 +714,10 @@
         <v>1</v>
       </c>
       <c r="B22" s="2">
-        <v>45669</v>
+        <v>45668</v>
       </c>
       <c r="C22" s="2">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>5</v>
@@ -731,7 +731,7 @@
         <v>45669</v>
       </c>
       <c r="C23" s="2">
-        <v>126</v>
+        <v>1847</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>5</v>
@@ -745,7 +745,7 @@
         <v>45663</v>
       </c>
       <c r="C24" s="2">
-        <v>98</v>
+        <v>6</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>5</v>
@@ -756,10 +756,10 @@
         <v>1</v>
       </c>
       <c r="B25" s="2">
-        <v>45665</v>
+        <v>45663</v>
       </c>
       <c r="C25" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>5</v>
@@ -770,13 +770,13 @@
         <v>1</v>
       </c>
       <c r="B26" s="2">
-        <v>45665</v>
+        <v>45663</v>
       </c>
       <c r="C26" s="2">
-        <v>226</v>
+        <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -784,13 +784,13 @@
         <v>1</v>
       </c>
       <c r="B27" s="2">
-        <v>45665</v>
+        <v>45664</v>
       </c>
       <c r="C27" s="2">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -798,13 +798,13 @@
         <v>1</v>
       </c>
       <c r="B28" s="2">
-        <v>45665</v>
+        <v>45664</v>
       </c>
       <c r="C28" s="2">
-        <v>115</v>
+        <v>2</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -812,10 +812,10 @@
         <v>1</v>
       </c>
       <c r="B29" s="2">
-        <v>45666</v>
+        <v>45665</v>
       </c>
       <c r="C29" s="2">
-        <v>94</v>
+        <v>167</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>5</v>
@@ -826,10 +826,10 @@
         <v>1</v>
       </c>
       <c r="B30" s="2">
-        <v>45668</v>
+        <v>45666</v>
       </c>
       <c r="C30" s="2">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>5</v>
@@ -840,13 +840,13 @@
         <v>1</v>
       </c>
       <c r="B31" s="2">
-        <v>45668</v>
+        <v>45666</v>
       </c>
       <c r="C31" s="2">
-        <v>268</v>
+        <v>21</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -854,10 +854,10 @@
         <v>1</v>
       </c>
       <c r="B32" s="2">
-        <v>45668</v>
+        <v>45666</v>
       </c>
       <c r="C32" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>5</v>
@@ -868,13 +868,13 @@
         <v>1</v>
       </c>
       <c r="B33" s="2">
-        <v>45669</v>
+        <v>45667</v>
       </c>
       <c r="C33" s="2">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -882,13 +882,13 @@
         <v>1</v>
       </c>
       <c r="B34" s="2">
-        <v>45663</v>
+        <v>45667</v>
       </c>
       <c r="C34" s="2">
-        <v>6</v>
+        <v>201</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -896,10 +896,10 @@
         <v>1</v>
       </c>
       <c r="B35" s="2">
-        <v>45663</v>
+        <v>45668</v>
       </c>
       <c r="C35" s="2">
-        <v>10</v>
+        <v>148</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>5</v>
@@ -910,10 +910,10 @@
         <v>1</v>
       </c>
       <c r="B36" s="2">
-        <v>45663</v>
+        <v>45669</v>
       </c>
       <c r="C36" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>5</v>
@@ -924,10 +924,10 @@
         <v>1</v>
       </c>
       <c r="B37" s="2">
-        <v>45664</v>
+        <v>45669</v>
       </c>
       <c r="C37" s="2">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>5</v>
@@ -938,13 +938,13 @@
         <v>1</v>
       </c>
       <c r="B38" s="2">
-        <v>45664</v>
+        <v>45669</v>
       </c>
       <c r="C38" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -952,10 +952,10 @@
         <v>1</v>
       </c>
       <c r="B39" s="2">
-        <v>45665</v>
+        <v>45663</v>
       </c>
       <c r="C39" s="2">
-        <v>167</v>
+        <v>98</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>5</v>
@@ -966,7 +966,7 @@
         <v>1</v>
       </c>
       <c r="B40" s="2">
-        <v>45666</v>
+        <v>45665</v>
       </c>
       <c r="C40" s="2">
         <v>3</v>
@@ -980,13 +980,13 @@
         <v>1</v>
       </c>
       <c r="B41" s="2">
-        <v>45666</v>
+        <v>45665</v>
       </c>
       <c r="C41" s="2">
-        <v>21</v>
+        <v>226</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -994,13 +994,13 @@
         <v>1</v>
       </c>
       <c r="B42" s="2">
-        <v>45666</v>
+        <v>45665</v>
       </c>
       <c r="C42" s="2">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1008,10 +1008,10 @@
         <v>1</v>
       </c>
       <c r="B43" s="2">
-        <v>45667</v>
+        <v>45665</v>
       </c>
       <c r="C43" s="2">
-        <v>1</v>
+        <v>115</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>5</v>
@@ -1022,13 +1022,13 @@
         <v>1</v>
       </c>
       <c r="B44" s="2">
-        <v>45667</v>
+        <v>45666</v>
       </c>
       <c r="C44" s="2">
-        <v>201</v>
+        <v>94</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1039,7 +1039,7 @@
         <v>45668</v>
       </c>
       <c r="C45" s="2">
-        <v>148</v>
+        <v>43</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>5</v>
@@ -1050,13 +1050,13 @@
         <v>1</v>
       </c>
       <c r="B46" s="2">
-        <v>45669</v>
+        <v>45668</v>
       </c>
       <c r="C46" s="2">
-        <v>1</v>
+        <v>268</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1064,10 +1064,10 @@
         <v>1</v>
       </c>
       <c r="B47" s="2">
-        <v>45669</v>
+        <v>45668</v>
       </c>
       <c r="C47" s="2">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>5</v>
@@ -1081,10 +1081,10 @@
         <v>45669</v>
       </c>
       <c r="C48" s="2">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1095,10 +1095,10 @@
         <v>45663</v>
       </c>
       <c r="C49" s="2">
-        <v>238</v>
+        <v>1071</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1109,7 +1109,7 @@
         <v>45663</v>
       </c>
       <c r="C50" s="2">
-        <v>899</v>
+        <v>3</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>5</v>
@@ -1120,10 +1120,10 @@
         <v>1</v>
       </c>
       <c r="B51" s="2">
-        <v>45664</v>
+        <v>45663</v>
       </c>
       <c r="C51" s="2">
-        <v>132</v>
+        <v>69</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>5</v>
@@ -1134,13 +1134,13 @@
         <v>1</v>
       </c>
       <c r="B52" s="2">
-        <v>45665</v>
+        <v>45664</v>
       </c>
       <c r="C52" s="2">
-        <v>5</v>
+        <v>219</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1148,13 +1148,13 @@
         <v>1</v>
       </c>
       <c r="B53" s="2">
-        <v>45665</v>
+        <v>45664</v>
       </c>
       <c r="C53" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1162,13 +1162,13 @@
         <v>1</v>
       </c>
       <c r="B54" s="2">
-        <v>45666</v>
+        <v>45665</v>
       </c>
       <c r="C54" s="2">
-        <v>236</v>
+        <v>1322</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1176,13 +1176,13 @@
         <v>1</v>
       </c>
       <c r="B55" s="2">
-        <v>45666</v>
+        <v>45665</v>
       </c>
       <c r="C55" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1190,13 +1190,13 @@
         <v>1</v>
       </c>
       <c r="B56" s="2">
-        <v>45667</v>
+        <v>45666</v>
       </c>
       <c r="C56" s="2">
-        <v>125</v>
+        <v>828</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1204,10 +1204,10 @@
         <v>1</v>
       </c>
       <c r="B57" s="2">
-        <v>45669</v>
+        <v>45666</v>
       </c>
       <c r="C57" s="2">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>5</v>
@@ -1218,13 +1218,13 @@
         <v>1</v>
       </c>
       <c r="B58" s="2">
-        <v>45669</v>
+        <v>45666</v>
       </c>
       <c r="C58" s="2">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1232,13 +1232,13 @@
         <v>1</v>
       </c>
       <c r="B59" s="2">
-        <v>45664</v>
+        <v>45667</v>
       </c>
       <c r="C59" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1246,10 +1246,10 @@
         <v>1</v>
       </c>
       <c r="B60" s="2">
-        <v>45664</v>
+        <v>45668</v>
       </c>
       <c r="C60" s="2">
-        <v>5</v>
+        <v>2250</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>5</v>
@@ -1260,13 +1260,13 @@
         <v>1</v>
       </c>
       <c r="B61" s="2">
-        <v>45665</v>
+        <v>45669</v>
       </c>
       <c r="C61" s="2">
-        <v>9</v>
+        <v>563</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1274,13 +1274,13 @@
         <v>1</v>
       </c>
       <c r="B62" s="2">
-        <v>45665</v>
+        <v>45669</v>
       </c>
       <c r="C62" s="2">
-        <v>995</v>
+        <v>3</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1288,10 +1288,10 @@
         <v>1</v>
       </c>
       <c r="B63" s="2">
-        <v>45666</v>
+        <v>45669</v>
       </c>
       <c r="C63" s="2">
-        <v>832</v>
+        <v>80</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>5</v>
@@ -1302,10 +1302,10 @@
         <v>1</v>
       </c>
       <c r="B64" s="2">
-        <v>45667</v>
+        <v>45663</v>
       </c>
       <c r="C64" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>5</v>
@@ -1316,10 +1316,10 @@
         <v>1</v>
       </c>
       <c r="B65" s="2">
-        <v>45667</v>
+        <v>45664</v>
       </c>
       <c r="C65" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>5</v>
@@ -1330,10 +1330,10 @@
         <v>1</v>
       </c>
       <c r="B66" s="2">
-        <v>45668</v>
+        <v>45664</v>
       </c>
       <c r="C66" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>5</v>
@@ -1344,13 +1344,13 @@
         <v>1</v>
       </c>
       <c r="B67" s="2">
-        <v>45668</v>
+        <v>45664</v>
       </c>
       <c r="C67" s="2">
-        <v>988</v>
+        <v>2</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1358,10 +1358,10 @@
         <v>1</v>
       </c>
       <c r="B68" s="2">
-        <v>45668</v>
+        <v>45666</v>
       </c>
       <c r="C68" s="2">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>5</v>
@@ -1372,10 +1372,10 @@
         <v>1</v>
       </c>
       <c r="B69" s="2">
-        <v>45669</v>
+        <v>45667</v>
       </c>
       <c r="C69" s="2">
-        <v>1847</v>
+        <v>5</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>5</v>
@@ -1386,10 +1386,10 @@
         <v>1</v>
       </c>
       <c r="B70" s="2">
-        <v>45664</v>
+        <v>45667</v>
       </c>
       <c r="C70" s="2">
-        <v>751</v>
+        <v>41</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>5</v>
@@ -1400,10 +1400,10 @@
         <v>1</v>
       </c>
       <c r="B71" s="2">
-        <v>45664</v>
+        <v>45667</v>
       </c>
       <c r="C71" s="2">
-        <v>87</v>
+        <v>15</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>5</v>
@@ -1414,10 +1414,10 @@
         <v>1</v>
       </c>
       <c r="B72" s="2">
-        <v>45666</v>
+        <v>45668</v>
       </c>
       <c r="C72" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>5</v>
@@ -1428,10 +1428,10 @@
         <v>1</v>
       </c>
       <c r="B73" s="2">
-        <v>45667</v>
+        <v>45669</v>
       </c>
       <c r="C73" s="2">
-        <v>1406</v>
+        <v>3</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>5</v>
@@ -1442,13 +1442,13 @@
         <v>1</v>
       </c>
       <c r="B74" s="2">
-        <v>45667</v>
+        <v>45669</v>
       </c>
       <c r="C74" s="2">
-        <v>869</v>
+        <v>126</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -1456,13 +1456,13 @@
         <v>1</v>
       </c>
       <c r="B75" s="2">
-        <v>45667</v>
+        <v>45663</v>
       </c>
       <c r="C75" s="2">
-        <v>4</v>
+        <v>238</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -1470,10 +1470,10 @@
         <v>1</v>
       </c>
       <c r="B76" s="2">
-        <v>45667</v>
+        <v>45663</v>
       </c>
       <c r="C76" s="2">
-        <v>135</v>
+        <v>899</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>5</v>
@@ -1484,10 +1484,10 @@
         <v>1</v>
       </c>
       <c r="B77" s="2">
-        <v>45669</v>
+        <v>45664</v>
       </c>
       <c r="C77" s="2">
-        <v>14</v>
+        <v>132</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>5</v>
@@ -1498,13 +1498,13 @@
         <v>1</v>
       </c>
       <c r="B78" s="2">
-        <v>45663</v>
+        <v>45665</v>
       </c>
       <c r="C78" s="2">
-        <v>1071</v>
+        <v>5</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -1512,7 +1512,7 @@
         <v>1</v>
       </c>
       <c r="B79" s="2">
-        <v>45663</v>
+        <v>45665</v>
       </c>
       <c r="C79" s="2">
         <v>3</v>
@@ -1526,13 +1526,13 @@
         <v>1</v>
       </c>
       <c r="B80" s="2">
-        <v>45663</v>
+        <v>45666</v>
       </c>
       <c r="C80" s="2">
-        <v>69</v>
+        <v>236</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -1540,13 +1540,13 @@
         <v>1</v>
       </c>
       <c r="B81" s="2">
-        <v>45664</v>
+        <v>45666</v>
       </c>
       <c r="C81" s="2">
-        <v>219</v>
+        <v>4</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -1554,13 +1554,13 @@
         <v>1</v>
       </c>
       <c r="B82" s="2">
-        <v>45664</v>
+        <v>45667</v>
       </c>
       <c r="C82" s="2">
-        <v>4</v>
+        <v>125</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -1568,10 +1568,10 @@
         <v>1</v>
       </c>
       <c r="B83" s="2">
-        <v>45665</v>
+        <v>45669</v>
       </c>
       <c r="C83" s="2">
-        <v>1322</v>
+        <v>26</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>5</v>
@@ -1582,13 +1582,13 @@
         <v>1</v>
       </c>
       <c r="B84" s="2">
-        <v>45665</v>
+        <v>45669</v>
       </c>
       <c r="C84" s="2">
-        <v>1</v>
+        <v>173</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -1596,13 +1596,13 @@
         <v>1</v>
       </c>
       <c r="B85" s="2">
-        <v>45666</v>
+        <v>45664</v>
       </c>
       <c r="C85" s="2">
-        <v>828</v>
+        <v>751</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -1610,10 +1610,10 @@
         <v>1</v>
       </c>
       <c r="B86" s="2">
-        <v>45666</v>
+        <v>45664</v>
       </c>
       <c r="C86" s="2">
-        <v>4</v>
+        <v>87</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>5</v>
@@ -1627,7 +1627,7 @@
         <v>45666</v>
       </c>
       <c r="C87" s="2">
-        <v>133</v>
+        <v>2</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>5</v>
@@ -1641,10 +1641,10 @@
         <v>45667</v>
       </c>
       <c r="C88" s="2">
-        <v>8</v>
+        <v>1406</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -1652,13 +1652,13 @@
         <v>1</v>
       </c>
       <c r="B89" s="2">
-        <v>45668</v>
+        <v>45667</v>
       </c>
       <c r="C89" s="2">
-        <v>2250</v>
+        <v>869</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -1666,13 +1666,13 @@
         <v>1</v>
       </c>
       <c r="B90" s="2">
-        <v>45669</v>
+        <v>45667</v>
       </c>
       <c r="C90" s="2">
-        <v>563</v>
+        <v>4</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -1680,10 +1680,10 @@
         <v>1</v>
       </c>
       <c r="B91" s="2">
-        <v>45669</v>
+        <v>45667</v>
       </c>
       <c r="C91" s="2">
-        <v>3</v>
+        <v>135</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>5</v>
@@ -1697,7 +1697,7 @@
         <v>45669</v>
       </c>
       <c r="C92" s="2">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>5</v>
